--- a/main_df.xlsx
+++ b/main_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,180 +479,132 @@
           <t>Account</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ОФЗ 26238</t>
+          <t>ОФЗ 26243</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SU26238RMFS4</t>
+          <t>SU26243RMFS4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TQCB</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>20000</v>
+          <t>TQOB</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>50.7</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>20000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>395058</v>
-      </c>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>13KP3M</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ОФЗ 26243</t>
+          <t>ОФЗ 26244</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SU26243RMFS4</t>
+          <t>SU26244RMFS2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TQCB</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E3" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="F3" t="n">
-        <v>20000</v>
+          <t>TQOB</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>78.05</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>20000</v>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13KP3M</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ОФЗ 26244</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SU26244RMFS2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TQCB</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>101</v>
-      </c>
-      <c r="F4" t="n">
-        <v>50</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>50</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
           <t>395058/19V63</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ОФЗ 26243</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SU26243RMFS4</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TQCB</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>777</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>777777</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>777777</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>395058</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
